--- a/BBS report flow (version 1).xlsx
+++ b/BBS report flow (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITH\BBS-App\BBS-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2896B928-5A40-47B6-A8BD-390F94BBCBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ED46DD-CA7F-4974-974A-C3C66E230153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Report flow" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="126">
   <si>
     <t>รายชื่อของแต่ละทีมในกลุ่ม</t>
   </si>
@@ -502,6 +502,30 @@
   </si>
   <si>
     <t>ช่องเลือกกลุ่มเวลาเจอกลุ่มที่รายการยาวมันล้นจอ ทำให้พิมพ์ค้นหาได้</t>
+  </si>
+  <si>
+    <t>เพิ่มการแจ้งเตือนสำหรับ PWA</t>
+  </si>
+  <si>
+    <t>แจ้งเตือนไปยัง SHE - MANAGER เมื่อมีการรายงานใหม่เข้ามา</t>
+  </si>
+  <si>
+    <t>แจ้งเตือนไปยัง Employee เมื่อมีการ action form</t>
+  </si>
+  <si>
+    <t>แก้ไขจากเดิมอ่านค่า parameter จาก URL มาเป็นเก็บไว้ใน localstorage แทน</t>
+  </si>
+  <si>
+    <t>เพิ่มแถบ Menu bar สำหรับ มือถือ</t>
+  </si>
+  <si>
+    <t>แก้ไขปัญหาเรื่องการอัพโหลดไฟล์จากเดิมใช้ API ติด quota เปลี่ยนมาใช้ GS เป็น API แทน</t>
+  </si>
+  <si>
+    <t>ปรับหน้า LOGIN ให้มีความกว้างมากขึ้น</t>
+  </si>
+  <si>
+    <t>เปลี่ยนสูตรการคำนวณเป็นรายงานให้ครบ 12 ครั้งต่อเดือน</t>
   </si>
 </sst>
 </file>
@@ -12435,7 +12459,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F089E165-4FFF-4F75-95FD-A1C0AB852418}">
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="66"/>
@@ -12803,7 +12827,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E24" s="66">
         <v>7</v>
@@ -12938,7 +12962,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="66" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E33" s="66">
         <v>6</v>
@@ -13049,11 +13073,11 @@
       <c r="C40" s="66">
         <v>3</v>
       </c>
+      <c r="D40" s="66" t="s">
+        <v>73</v>
+      </c>
       <c r="E40" s="66">
         <v>2</v>
-      </c>
-      <c r="F40" s="66" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -13071,6 +13095,121 @@
       </c>
       <c r="E41" s="66">
         <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="66">
+        <v>41</v>
+      </c>
+      <c r="B42" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="66">
+        <v>2</v>
+      </c>
+      <c r="E42" s="66">
+        <v>1</v>
+      </c>
+      <c r="F42" s="66" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="66">
+        <v>42</v>
+      </c>
+      <c r="B43" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="66">
+        <v>2</v>
+      </c>
+      <c r="E43" s="66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="66">
+        <v>43</v>
+      </c>
+      <c r="B44" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="66">
+        <v>2</v>
+      </c>
+      <c r="E44" s="66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="66">
+        <v>44</v>
+      </c>
+      <c r="B45" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="66">
+        <v>3</v>
+      </c>
+      <c r="D45" s="66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="66">
+        <v>45</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="66">
+        <v>2</v>
+      </c>
+      <c r="D46" s="66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="66">
+        <v>46</v>
+      </c>
+      <c r="B47" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="66">
+        <v>3</v>
+      </c>
+      <c r="D47" s="66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="66">
+        <v>47</v>
+      </c>
+      <c r="B48" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="66">
+        <v>1</v>
+      </c>
+      <c r="D48" s="66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="66">
+        <v>48</v>
+      </c>
+      <c r="B49" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="66">
+        <v>3</v>
+      </c>
+      <c r="D49" s="66" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/BBS report flow (version 1).xlsx
+++ b/BBS report flow (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITH\BBS-App\BBS-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02ED46DD-CA7F-4974-974A-C3C66E230153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B225ACB9-4D44-424F-AB32-1ED5D0262787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="127">
   <si>
     <t>รายชื่อของแต่ละทีมในกลุ่ม</t>
   </si>
@@ -526,6 +526,9 @@
   </si>
   <si>
     <t>เปลี่ยนสูตรการคำนวณเป็นรายงานให้ครบ 12 ครั้งต่อเดือน</t>
+  </si>
+  <si>
+    <t>เปลี่ยนเสียงการแจ้งเตือนเฉพาะแอพ</t>
   </si>
 </sst>
 </file>
@@ -12459,7 +12462,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F089E165-4FFF-4F75-95FD-A1C0AB852418}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="66"/>
@@ -13107,11 +13110,11 @@
       <c r="C42" s="66">
         <v>2</v>
       </c>
+      <c r="D42" s="66" t="s">
+        <v>73</v>
+      </c>
       <c r="E42" s="66">
         <v>1</v>
-      </c>
-      <c r="F42" s="66" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -13127,6 +13130,9 @@
       <c r="E43" s="66">
         <v>2</v>
       </c>
+      <c r="F43" s="66" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="66">
@@ -13198,7 +13204,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:5">
       <c r="A49" s="66">
         <v>48</v>
       </c>
@@ -13210,6 +13216,20 @@
       </c>
       <c r="D49" s="66" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="66">
+        <v>49</v>
+      </c>
+      <c r="B50" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="66">
+        <v>1</v>
+      </c>
+      <c r="E50" s="66">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/BBS report flow (version 1).xlsx
+++ b/BBS report flow (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITH\BBS-App\BBS-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B225ACB9-4D44-424F-AB32-1ED5D0262787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79A3C3B-FB95-460C-B192-E4C1190D2221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="126">
   <si>
     <t>รายชื่อของแต่ละทีมในกลุ่ม</t>
   </si>
@@ -466,9 +466,6 @@
   </si>
   <si>
     <t>ตัวเลือกแผนกมาไม่ครบ</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>เพิ่มตารางจัดการการรายงานของ SHE</t>
@@ -12928,7 +12925,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C31" s="66">
         <v>2</v>
@@ -12959,7 +12956,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C33" s="66">
         <v>2</v>
@@ -12976,13 +12973,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" s="65">
         <v>2</v>
       </c>
       <c r="D34" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E34" s="65">
         <v>2</v>
@@ -12994,13 +12991,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="87" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C35" s="65">
         <v>2</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E35" s="65">
         <v>4</v>
@@ -13012,7 +13009,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="67" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" s="66">
         <v>2</v>
@@ -13026,7 +13023,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C37" s="66">
         <v>3</v>
@@ -13040,7 +13037,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C38" s="66">
         <v>3</v>
@@ -13054,7 +13051,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="67" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="66">
         <v>3</v>
@@ -13071,7 +13068,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="67" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" s="66">
         <v>3</v>
@@ -13088,7 +13085,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C41" s="66">
         <v>2</v>
@@ -13105,7 +13102,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C42" s="66">
         <v>2</v>
@@ -13122,16 +13119,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="67" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C43" s="66">
         <v>2</v>
       </c>
+      <c r="D43" s="66" t="s">
+        <v>73</v>
+      </c>
       <c r="E43" s="66">
-        <v>2</v>
-      </c>
-      <c r="F43" s="66" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -13139,13 +13136,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C44" s="66">
         <v>2</v>
       </c>
+      <c r="D44" s="66" t="s">
+        <v>73</v>
+      </c>
       <c r="E44" s="66">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -13153,7 +13153,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="67" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C45" s="66">
         <v>3</v>
@@ -13167,7 +13167,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C46" s="66">
         <v>2</v>
@@ -13181,7 +13181,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" s="66">
         <v>3</v>
@@ -13195,7 +13195,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" s="66">
         <v>1</v>
@@ -13209,7 +13209,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C49" s="66">
         <v>3</v>
@@ -13223,10 +13223,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="67" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C50" s="66">
         <v>1</v>
+      </c>
+      <c r="D50" s="66" t="s">
+        <v>73</v>
       </c>
       <c r="E50" s="66">
         <v>4</v>

--- a/BBS report flow (version 1).xlsx
+++ b/BBS report flow (version 1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITH\BBS-App\BBS-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79A3C3B-FB95-460C-B192-E4C1190D2221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5847CD8-3EE4-4B6D-8957-920019DD0980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="128">
   <si>
     <t>รายชื่อของแต่ละทีมในกลุ่ม</t>
   </si>
@@ -526,6 +526,12 @@
   </si>
   <si>
     <t>เปลี่ยนเสียงการแจ้งเตือนเฉพาะแอพ</t>
+  </si>
+  <si>
+    <t>เมื่อกรอกรหัสพนักงานให้ setlocalstorage เลย</t>
+  </si>
+  <si>
+    <t>แก้ไขปัญหา net ฝั่งประเทศลาวใช้งานไม่ได้</t>
   </si>
 </sst>
 </file>
@@ -12459,7 +12465,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F089E165-4FFF-4F75-95FD-A1C0AB852418}">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="66"/>
@@ -13235,6 +13241,31 @@
         <v>4</v>
       </c>
     </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="66">
+        <v>50</v>
+      </c>
+      <c r="B51" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="66">
+        <v>3</v>
+      </c>
+      <c r="D51" s="66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="66">
+        <v>51</v>
+      </c>
+      <c r="B52" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="66">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G38" xr:uid="{F089E165-4FFF-4F75-95FD-A1C0AB852418}"/>
   <conditionalFormatting sqref="A2:F95">

--- a/BBS report flow (version 1).xlsx
+++ b/BBS report flow (version 1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITH\BBS-App\BBS-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5847CD8-3EE4-4B6D-8957-920019DD0980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087B72C2-F765-46BB-BD3B-1D20067A0CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Report flow" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="137">
   <si>
     <t>รายชื่อของแต่ละทีมในกลุ่ม</t>
   </si>
@@ -532,6 +532,33 @@
   </si>
   <si>
     <t>แก้ไขปัญหา net ฝั่งประเทศลาวใช้งานไม่ได้</t>
+  </si>
+  <si>
+    <t>ทำให้แจ้งเตือนเมื่อไม่ได้เปิดแอพ</t>
+  </si>
+  <si>
+    <t>ปรับ Element สำหรับหน้าจอมือถือ เพราะตอนนี้ยังมีล้นจออยู่</t>
+  </si>
+  <si>
+    <t>ปิดการแสดงรายชื่อแบบกลุ่มเปลี่ยนเป็นแสดงแบบ popup แทนและสรุปให้รูปว่าในกลุ่มใครส่งกี่ครั้ง</t>
+  </si>
+  <si>
+    <t>เอาแจ้งเตือนแบบ log ออกให้ใช้แบบแจ้งโดยตรงแทน</t>
+  </si>
+  <si>
+    <t>แก้ไขการ export ไฟล์สรุปการจ่ายเงินใหม่ให้ list ออกมา ให้ครบทุกรายชื่อตามของแต่ละกลุ่ม</t>
+  </si>
+  <si>
+    <t>Dashboard/สรุปจ่ายเงิน</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>Dashboard/รายงานทั้งหมด</t>
+  </si>
+  <si>
+    <t>เพิ่มสรุปรายงานทั้งหมดโดยการแยกออกมาเป็น 4 หัวข้อหลัง - (safe/unsafe)เป็นจำนวนเท่าไหร่ของแต่ละหัวข้อ</t>
   </si>
 </sst>
 </file>
@@ -12465,11 +12492,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F089E165-4FFF-4F75-95FD-A1C0AB852418}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="66"/>
-    <col min="2" max="2" width="90.625" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="110.375" style="67" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.75" style="66" customWidth="1"/>
     <col min="4" max="4" width="11.125" style="66" customWidth="1"/>
     <col min="5" max="5" width="9" style="66"/>
@@ -13210,7 +13237,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:7">
       <c r="A49" s="66">
         <v>48</v>
       </c>
@@ -13224,7 +13251,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:7">
       <c r="A50" s="66">
         <v>49</v>
       </c>
@@ -13241,7 +13268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:7">
       <c r="A51" s="66">
         <v>50</v>
       </c>
@@ -13255,7 +13282,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:7">
       <c r="A52" s="66">
         <v>51</v>
       </c>
@@ -13264,6 +13291,123 @@
       </c>
       <c r="C52" s="66">
         <v>4</v>
+      </c>
+      <c r="D52" s="66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="66">
+        <v>52</v>
+      </c>
+      <c r="B53" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="66">
+        <v>1</v>
+      </c>
+      <c r="E53" s="66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="66">
+        <v>53</v>
+      </c>
+      <c r="B54" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" s="66">
+        <v>1</v>
+      </c>
+      <c r="D54" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="66">
+        <v>5</v>
+      </c>
+      <c r="G54" s="66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="66">
+        <v>54</v>
+      </c>
+      <c r="B55" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="66">
+        <v>3</v>
+      </c>
+      <c r="D55" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="66">
+        <v>2</v>
+      </c>
+      <c r="G55" s="66" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="66">
+        <v>55</v>
+      </c>
+      <c r="B56" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="66">
+        <v>1</v>
+      </c>
+      <c r="D56" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="66">
+        <v>4</v>
+      </c>
+      <c r="G56" s="66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="66">
+        <v>56</v>
+      </c>
+      <c r="B57" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="66">
+        <v>3</v>
+      </c>
+      <c r="D57" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="66">
+        <v>1</v>
+      </c>
+      <c r="G57" s="66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="66">
+        <v>57</v>
+      </c>
+      <c r="B58" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="66">
+        <v>2</v>
+      </c>
+      <c r="D58" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="66">
+        <v>3</v>
+      </c>
+      <c r="G58" s="66" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/BBS report flow (version 1).xlsx
+++ b/BBS report flow (version 1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITH\BBS-App\BBS-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087B72C2-F765-46BB-BD3B-1D20067A0CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59E1DF0-AA91-46AB-A207-445B97AA71D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FFFA8B83-F3A6-483C-B4BA-3B030823B3B1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="141">
   <si>
     <t>รายชื่อของแต่ละทีมในกลุ่ม</t>
   </si>
@@ -559,6 +559,24 @@
   </si>
   <si>
     <t>เพิ่มสรุปรายงานทั้งหมดโดยการแยกออกมาเป็น 4 หัวข้อหลัง - (safe/unsafe)เป็นจำนวนเท่าไหร่ของแต่ละหัวข้อ</t>
+  </si>
+  <si>
+    <t>ปรับหน้าตาของหน้าแรก</t>
+  </si>
+  <si>
+    <t>ปรับหน้า สถิติรายงาน</t>
+  </si>
+  <si>
+    <t>แก้ไขการแสดงผลหน้า รายงานการจ่ายเงิน
+-ให้ดูง่ายขึ้น
+-จัดกลุ่มชุดเจน
+-ดูประวัติการรายงานได้ด้วยการ click ชื่อ 
+-กรอกค่าได้ all / ได้รับเงิน / ไม่ได้รับเงิน
+-แสดงรายชื่อพนักงานของแต่ละกลุ่มย่อยโดยนับตามเดือนที่เลือกดู
+-สามารถดูการรายงานจาก She หาก User คนไหนโดน She รายงานเข้ามาในเดือนนั้น</t>
+  </si>
+  <si>
+    <t>5-7/12/2025</t>
   </si>
 </sst>
 </file>
@@ -945,7 +963,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1068,6 +1086,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12492,7 +12514,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F089E165-4FFF-4F75-95FD-A1C0AB852418}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="66"/>
@@ -12502,7 +12524,7 @@
     <col min="5" max="5" width="9" style="66"/>
     <col min="6" max="6" width="9" style="66" customWidth="1"/>
     <col min="7" max="7" width="37.75" style="66" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="66"/>
+    <col min="8" max="8" width="11" style="66" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="67.75" style="66" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.5" style="66" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" style="66" bestFit="1" customWidth="1"/>
@@ -13237,7 +13259,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:8">
       <c r="A49" s="66">
         <v>48</v>
       </c>
@@ -13251,7 +13273,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:8">
       <c r="A50" s="66">
         <v>49</v>
       </c>
@@ -13268,7 +13290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:8">
       <c r="A51" s="66">
         <v>50</v>
       </c>
@@ -13282,7 +13304,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:8">
       <c r="A52" s="66">
         <v>51</v>
       </c>
@@ -13296,7 +13318,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:8">
       <c r="A53" s="66">
         <v>52</v>
       </c>
@@ -13306,11 +13328,17 @@
       <c r="C53" s="66">
         <v>1</v>
       </c>
+      <c r="D53" s="66" t="s">
+        <v>73</v>
+      </c>
       <c r="E53" s="66">
         <v>6</v>
       </c>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="H53" s="91">
+        <v>45998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="66">
         <v>53</v>
       </c>
@@ -13330,7 +13358,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:8">
       <c r="A55" s="66">
         <v>54</v>
       </c>
@@ -13350,7 +13378,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:8">
       <c r="A56" s="66">
         <v>55</v>
       </c>
@@ -13370,7 +13398,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:8">
       <c r="A57" s="66">
         <v>56</v>
       </c>
@@ -13390,7 +13418,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:8">
       <c r="A58" s="66">
         <v>57</v>
       </c>
@@ -13408,6 +13436,60 @@
       </c>
       <c r="G58" s="66" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="66">
+        <v>58</v>
+      </c>
+      <c r="B59" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="66">
+        <v>1</v>
+      </c>
+      <c r="D59" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="G59" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="H59" s="91" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="66">
+        <v>59</v>
+      </c>
+      <c r="B60" s="67" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="66">
+        <v>1</v>
+      </c>
+      <c r="D60" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="H60" s="91" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="126">
+      <c r="A61" s="66">
+        <v>60</v>
+      </c>
+      <c r="B61" s="90" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="66">
+        <v>4</v>
+      </c>
+      <c r="D61" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" s="91" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
